--- a/data/trans_camb/IP1016-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP1016-Habitat-trans_camb.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,03</t>
+          <t>0,0; 2,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,45</t>
+          <t>0,0; 1,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,15</t>
+          <t>0,0; 0,91</t>
         </is>
       </c>
     </row>
@@ -1270,17 +1270,17 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,46</t>
+          <t>0,0; 0,57</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,27</t>
+          <t>0,0; 0,24</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,27</t>
+          <t>0,0; 0,3</t>
         </is>
       </c>
     </row>
